--- a/Vergelijking_oplossingsmethoden.xlsx
+++ b/Vergelijking_oplossingsmethoden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_CD184E4D845A1B86662F8493F56C158C85DF95CA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83C77058-8BFC-46BC-82CD-44FECF77BE95}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_CD184E4D845A1B86662F8493F56C158C85DF95CA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CBB284-8365-4E7F-8C39-27E15C188E48}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>Methode</t>
   </si>
@@ -151,7 +151,16 @@
     <t>Aantal machines</t>
   </si>
   <si>
+    <t>methode</t>
+  </si>
+  <si>
     <t>Vóór Improving</t>
+  </si>
+  <si>
+    <t>Vóór Improving (s)</t>
+  </si>
+  <si>
+    <t>Na Improving (s)</t>
   </si>
 </sst>
 </file>
@@ -283,7 +292,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8AED4BB3-519B-45CA-A0F8-AF692694BCA4}" type="CELLRANGE">
+                    <a:fld id="{66781A49-9433-4542-B989-51CD79B382FB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -317,7 +326,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{06FE7F60-19D5-4F0E-B8C4-C03D371014B7}" type="CELLRANGE">
+                    <a:fld id="{E3D7E9D9-7E56-45F2-94CE-F8A86C070967}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -483,7 +492,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13AA90E0-47D4-4CD0-9D71-07156B193982}" type="CELLRANGE">
+                    <a:fld id="{1D42C573-86FB-42EA-91C0-B26D659B0C53}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -517,7 +526,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A40D7EC2-8A23-4043-9363-658FD3BF3E2A}" type="CELLRANGE">
+                    <a:fld id="{8FF6B472-23B0-424D-96D9-7C7ABA05F011}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -989,7 +998,769 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.880319596216045E-2"/>
+          <c:y val="8.0514607593653822E-2"/>
+          <c:w val="0.90286351706036749"/>
+          <c:h val="0.73577136191309422"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafieken!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vóór Improving</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BDFF0F7F-8217-43ED-99CB-804C0CE8C44E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-F2CD-4407-95CD-76874D05D5F4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{4D4464FD-8EF8-4F38-97F5-D32F12396ED0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-F2CD-4407-95CD-76874D05D5F4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafieken!$B$19:$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Greedy</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Simulated Annealing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafieken!$B$20:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.92E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.875034679999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Grafieken!$B$20:$C$20</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="2"/>
+                  <c:pt idx="0">
+                    <c:v>0,000192</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>36,87503468</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F2CD-4407-95CD-76874D05D5F4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafieken!$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Na Improving</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{06F1EE54-86E4-4513-9D72-04F244B59B83}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-F2CD-4407-95CD-76874D05D5F4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B3B51A35-1754-4A3E-8BBC-CAF569212CE9}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-F2CD-4407-95CD-76874D05D5F4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafieken!$B$19:$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Greedy</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Simulated Annealing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafieken!$B$21:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.21549660000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.899143420000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Grafieken!$B$21:$C$21</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="2"/>
+                  <c:pt idx="0">
+                    <c:v>0,2154966</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>36,89914342</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F2CD-4407-95CD-76874D05D5F4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="267"/>
+        <c:overlap val="-43"/>
+        <c:axId val="1818058863"/>
+        <c:axId val="1904064719"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1818058863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1904064719"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1904064719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL" sz="1200"/>
+                  <a:t>Gemiddelde rekentijd</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.2385830196202432E-2"/>
+              <c:y val="0.31163208946707749"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1818058863"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1578,20 +2349,569 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="208">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>285749</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>352424</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>542924</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1611,6 +2931,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533399</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A9ECCA2-5F9E-00BB-AEA3-978A38C1D3D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2337,12 +3693,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="25.140625" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -2445,7 +3799,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>3597.7499999999991</v>
@@ -2470,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -2496,6 +3850,72 @@
       </c>
       <c r="C13" s="2">
         <v>43.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.92E-4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.21549660000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2">
+        <v>36.875034679999999</v>
+      </c>
+      <c r="C17" s="2">
+        <v>36.899143420000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.92E-4</v>
+      </c>
+      <c r="C20" s="2">
+        <v>36.875034679999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.21549660000000001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>36.899143420000001</v>
       </c>
     </row>
   </sheetData>
